--- a/docs/deliverables/out/Programme/Comparisons/BIBS_Comparison_BRD-06_BDOI_FRS_vs_BIBS_FRS_Renewal_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Comparisons/BIBS_Comparison_BRD-06_BDOI_FRS_vs_BIBS_FRS_Renewal_v1.0.xlsx
@@ -5963,7 +5963,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Same: 13, Partial: 57, Different: 18, Not in ours: 55</t>
+          <t>Same: 12, Partial: 58, Different: 18, Not in ours: 55</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr"/>
@@ -60906,7 +60906,7 @@
       </c>
       <c r="G71" s="29" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/Comparisons/BIBS_Comparison_BRD-06_BDOI_FRS_vs_BIBS_FRS_Renewal_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Comparisons/BIBS_Comparison_BRD-06_BDOI_FRS_vs_BIBS_FRS_Renewal_v1.0.xlsx
@@ -1594,7 +1594,7 @@
       </c>
       <c r="I8" s="29" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Decide</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="I9" s="29" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Decide</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Only in ours: 43 items; conflicting: 28 points, of which 17 where the BIBS FRS follows the BRD or the platform</t>
+          <t>Only in ours: 43 items; conflicting: 28 points, of which 15 where the BIBS FRS follows the BRD or the platform</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/Comparisons/BIBS_Comparison_BRD-06_BDOI_FRS_vs_BIBS_FRS_Renewal_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Comparisons/BIBS_Comparison_BRD-06_BDOI_FRS_vs_BIBS_FRS_Renewal_v1.0.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="13" state="hidden" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$70</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary and recommendation'!$A$4:$D$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary and recommendation'!$4:$4</definedName>
@@ -38,7 +38,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Only in ours'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Only in BDOI''s'!$A$4:$F$107</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Only in BDOI''s'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Conflicts'!$A$4:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Conflicts'!$A$4:$L$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Conflicts'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Annex comparison'!$A$4:$E$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Annex comparison'!$4:$4</definedName>
@@ -1310,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1323,6 +1323,8 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1350,6 +1352,8 @@
       <c r="H3" s="27" t="n"/>
       <c r="I3" s="27" t="n"/>
       <c r="J3" s="27" t="n"/>
+      <c r="K3" s="27" t="n"/>
+      <c r="L3" s="27" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="28" t="inlineStr">
@@ -1400,6 +1404,16 @@
       <c r="J4" s="28" t="inlineStr">
         <is>
           <t>Our recommendation</t>
+        </is>
+      </c>
+      <c r="K4" s="28" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L4" s="28" t="inlineStr">
+        <is>
+          <t>Setting in BIBS</t>
         </is>
       </c>
     </row>
@@ -1452,6 +1466,16 @@
           <t>Keep Clean / Review / Exception as the BRD says; show the Not for Renewal accounts as BDOI's "Non-Renewable" panel (a filter on the disposition).</t>
         </is>
       </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>the third panel of the renewal accounts is Non-Renewable (default, BDOI's panels Clean, Review, Non-Renewable and All, the Exception accounts shown under Review) or Exception (the BRD's Clean, Review and Exception).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
@@ -1502,6 +1526,16 @@
           <t>Keep the Review bucket (the TSU route is manual work) and use BDOI's disposition word once the For Quotation / For Proposal meaning is settled.</t>
         </is>
       </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>an account above the sum insured threshold is Clean For Quotation and goes to the TSU (default, BDOI's rule) or Review with a proposal for the TSU.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
@@ -1552,6 +1586,12 @@
           <t>Adopt BDOI's meaning (BDOI's process vocabulary) after Marketing confirms it; the platform change is the routing of the two values.</t>
         </is>
       </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
@@ -1602,6 +1642,12 @@
           <t>Ask BDOI which of its two rules applies; we recommend Annex C (renew in the open market) as the detailed rule, with the change of account type.</t>
         </is>
       </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
@@ -1652,6 +1698,12 @@
           <t>Ask BDOI; take RMU from the AO code list if LAMD sends the full loan list (FRRN.012).</t>
         </is>
       </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
@@ -1702,6 +1754,16 @@
           <t>Keep the TL assignment of the BRD and add automatic assignment as an option per segment (platform change), if BDOI confirms.</t>
         </is>
       </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>the renewal accounts of the market segments chosen are assigned automatically to an Account Officer of the team, fewest open accounts first and then in turn, and the accounts routed to Processing to a Processing Officer when a second setting is on; with no segment chosen (default, the BRD) the Team Leader assigns.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
@@ -1752,6 +1814,16 @@
           <t>Keep the BRD transfer; add BDOI's referral as a second action (New Business opportunity) if BDOI wants both.</t>
         </is>
       </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>a transfer to another Marketing unit is a referral (the receiving unit opens a New Business account and the renewal keeps its owner, BDOI's text), a move of the account (the BRD), or both offered to the user (default).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
@@ -1802,6 +1874,12 @@
           <t>Keep both triggers; BDOI confirms the lead days per segment.</t>
         </is>
       </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
@@ -1852,6 +1930,12 @@
           <t>Keep ours; use BDOI's status names on the renewal record (In Process Renewal for an initiated renewal).</t>
         </is>
       </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
@@ -1902,6 +1986,12 @@
           <t>Adopt BDOI's nine values as a list mapped to the three BRD outcomes, with BDOI's bucket and disposition per value (platform change).</t>
         </is>
       </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
@@ -1952,6 +2042,16 @@
           <t>Keep the RA lock of the BRD and add BDOI's lock after placement (edits after placement are already refused by the account).</t>
         </is>
       </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>Marketing can no longer change the account once the Renewal Advice is generated (default, BDOI's text) or once it is posted and the placement is sent.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
@@ -2002,6 +2102,16 @@
           <t>Adopt BDOI's durations as parameters now; automatic requests and extensions are a platform change for BDOI to prioritise.</t>
         </is>
       </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>hold cover durations of 30 days (Non-CBG), 90 days (CBG), 60 days (CBG Motor after an insurer's rejection) and 30 days (CBG Home), extensions of 15 or 30 days from 7 days before the end, automatic requests for Non-CBG accounts after the client's confirmation and for Clean CBG accounts 75 days before expiry, and the monthly CBG Home extension on the 15th; each value is a setting.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
@@ -2052,6 +2162,16 @@
           <t>Adopt BDOI's 75 / 45 days and the automatic determination; name the notices First and Final as in the approved templates.</t>
         </is>
       </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>the Renewal Advice notice follows the expiry, First Notice from 75 days and Last Notice from 45 days before expiry (default, BDOI's text), or is chosen by the user.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
@@ -2102,6 +2222,12 @@
           <t>Adopt BDOI's definition and 75 days (parameter value).</t>
         </is>
       </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
@@ -2152,6 +2278,16 @@
           <t>Keep the mutual exclusion and the effective expiry date of the BRD; adopt BDOI's day offsets (1 and 3 days) as parameters.</t>
         </is>
       </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>the No Advice Letter 1 day and the Non-Renewal Letter 1 day (CBG Motor) or 3 days (Non-CBG) after the effective expiry date, each a setting; the two letters exclude each other.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
@@ -2202,6 +2338,16 @@
           <t>Adopt BDOI's convention (answers Q07); platform change of the password rule.</t>
         </is>
       </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>protected files use BDOI's password convention (default: the first three letters of the first and last names in capitals for an individual client, eight random characters for a corporate client) or a random password per file.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
@@ -2252,6 +2398,16 @@
           <t>BDO ITG decides whether CCM and MFT are in scope for go-live; BIBS keeps e-mail as the fallback channel.</t>
         </is>
       </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>client documents are sent through CCM (default) or by protected e-mail with the password in a separate e-mail; insurers receive their files through MFT when enrolled, otherwise by e-mail.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
@@ -2302,6 +2458,12 @@
           <t>Keep ours; align BDOI's wording with BRRN.041.</t>
         </is>
       </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
@@ -2352,6 +2514,12 @@
           <t>Ask BDOI which timing it means; both are parameter values.</t>
         </is>
       </c>
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
@@ -2402,6 +2570,16 @@
           <t>Keep the booking a user action as the Walkthrough addendum says, unless BDOI changes it.</t>
         </is>
       </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>the insurer's approval of the placement leaves the account For Booking for the Processing Officer (default, the BRD) or books and locks it (BDOI's text).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
@@ -2452,6 +2630,16 @@
           <t>Keep ours and add BDOI's Review routing for endorsements of the term if Marketing wants to see them.</t>
         </is>
       </c>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>every endorsement of the expiring term routes the account to Review (default, BDOI's text) or only an endorsement in progress.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
@@ -2502,6 +2690,16 @@
           <t>Keep the five dispositions of the BRD and add BDOI's eleven extra reasons as list values.</t>
         </is>
       </c>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>the dispositions offered to Marketing are For Renewal, Not for Renewal, For Quotation, For Proposal and Lost Business (default, the BRD) or the first four with Lost Business as a reason of Not for Renewal (BDOI's text); BDOI's non-renewal reasons are in the list of values.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
@@ -2552,6 +2750,16 @@
           <t>Ask BDOI; a second approval is a platform change and slows BRRN.040.</t>
         </is>
       </c>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>an accepted account goes to the payment check and placement at once (default, the BRD) or is Submitted for Approval and goes to placement once an approver approves it (BDOI's text).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
@@ -2602,6 +2810,16 @@
           <t>Keep the matrix and load BDOI's rule (Clean is automatic For Renewal) as its first content.</t>
         </is>
       </c>
+      <c r="K28" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>Clean accounts are disposed For Renewal automatically (default, BDOI's rule) or wait for the disposition of Marketing.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n">
@@ -2652,6 +2870,16 @@
           <t>Map the two lists one to one in the status model annex and use BDOI's names where the BRD is silent.</t>
         </is>
       </c>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>the statuses read with BDOI's names (default: In Process Renewal, Submitted for Posting, Posted and the others) or with the workflow stage names.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n">
@@ -2702,6 +2930,16 @@
           <t>Use BDOI's names RMEL and NRL in the merged FRS and on the screens.</t>
         </is>
       </c>
+      <c r="K30" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>generated files are named with BDOI's convention &lt;Product&gt;_&lt;Letter&gt;_&lt;Reference&gt;_MMDDYYYY.pdf (default) or with the letter number.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
@@ -2752,6 +2990,16 @@
           <t>Keep the BRD label and correct BDOI's two variants.</t>
         </is>
       </c>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>Configurable - BDOI to confirm the setting</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>the reason recorded for a non-renewable risk code is Non-renewable Accounts (default, the BRD) or Non-Renewable Risk Code (BDOI's text).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
@@ -2802,11 +3050,17 @@
           <t>Adopt BDOI's automatic status change; the placement itself stays a user action.</t>
         </is>
       </c>
+      <c r="K32" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J32"/>
+  <autoFilter ref="A4:L32"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="I5:I532">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="4" stopIfTrue="1">
@@ -2816,7 +3070,7 @@
       <formula>"Decide"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J532">
+  <conditionalFormatting sqref="A5:L532">
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -4494,7 +4748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5528,17 +5782,17 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>Annex comparison</t>
+          <t>Conflicts</t>
         </is>
       </c>
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>BDOI annex</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Annex of BDOI's FRS</t>
+          <t>Open, or Configurable when BIBS offers both readings</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr"/>
@@ -5546,17 +5800,17 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Annex comparison</t>
+          <t>Conflicts</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Setting in BIBS</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Rule, layout or template</t>
+          <t>The system setting that chooses the reading, with its default</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr"/>
@@ -5569,12 +5823,12 @@
       </c>
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>BDOI's FRS</t>
+          <t>BDOI annex</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Content of the annex</t>
+          <t>Annex of BDOI's FRS</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr"/>
@@ -5587,12 +5841,12 @@
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>BIBS FRS and platform</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>What the BIBS FRS and platform have</t>
+          <t>Rule, layout or template</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr"/>
@@ -5605,12 +5859,12 @@
       </c>
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>BDOI's FRS</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>Content of the annex</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr"/>
@@ -5618,17 +5872,17 @@
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>Incorporation plan</t>
+          <t>Annex comparison</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>BIBS FRS and platform</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Order of work</t>
+          <t>What the BIBS FRS and platform have</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
@@ -5636,17 +5890,17 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>Incorporation plan</t>
+          <t>Annex comparison</t>
         </is>
       </c>
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>BDOI section</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Section of BDOI's FRS that receives the content</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr"/>
@@ -5659,12 +5913,12 @@
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>Content to insert from ours</t>
+          <t>Step</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>BIBS content and how it is placed</t>
+          <t>Order of work</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr"/>
@@ -5677,12 +5931,12 @@
       </c>
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>Form in BDOI's style</t>
+          <t>BDOI section</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>How it looks in BDOI's FRS</t>
+          <t>Section of BDOI's FRS that receives the content</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr"/>
@@ -5695,12 +5949,12 @@
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>Effort (days)</t>
+          <t>Content to insert from ours</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Estimated person-days of the project team (BDOI's effort apart)</t>
+          <t>BIBS content and how it is placed</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr"/>
@@ -5713,18 +5967,54 @@
       </c>
       <c r="B68" s="25" t="inlineStr">
         <is>
+          <t>Form in BDOI's style</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>How it looks in BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>Incorporation plan</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>Effort (days)</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Estimated person-days of the project team (BDOI's effort apart)</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Incorporation plan</t>
+        </is>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
           <t>Who</t>
         </is>
       </c>
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C70" s="14" t="inlineStr">
         <is>
           <t>Who does it and who reviews</t>
         </is>
       </c>
-      <c r="D68" s="14" t="inlineStr"/>
+      <c r="D70" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D68"/>
+  <autoFilter ref="A4:D70"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
